--- a/杭州天猫.xlsx
+++ b/杭州天猫.xlsx
@@ -71,11 +71,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -453,7 +454,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -514,6 +515,55 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>汤嘉仪</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>杭州天猫</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>数据分析实习生</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026.07.15</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026.08.15</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1个月</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>待入职</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>女；微信:tangjiayi8888；邮箱:tangjiayi20050427@163.com；尽快对接流程发offer</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>汤嘉仪个人简历.docx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
